--- a/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260220.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260220.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,6 +653,174 @@
         <v>77.3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>29422</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cont Salad - 32oz Sabert (Round)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>63.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>41788</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Container - Anchor (16oz)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>41789</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Container - Anchor (24oz)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="E14" t="n">
+        <v>44.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>41399</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cup - Cold (12oz)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="E15" t="n">
+        <v>84.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>41792</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lid Anchor - 16/24oz (Dome)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="E16" t="n">
+        <v>40.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>41800</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lid Anchor - 16/24oz (Flat)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>52.76</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52.76</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2686</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lid Salad - 24/32oz Sabert (Round)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="E18" t="n">
+        <v>46.76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>40007</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Bowl (Smoothie)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="E19" t="n">
+        <v>35.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
